--- a/reports/pdf_rolling5_20260630.xlsx
+++ b/reports/pdf_rolling5_20260630.xlsx
@@ -745,7 +745,7 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>삼현  (편출)</t>
+          <t>에이프릴바이오  (편출)</t>
         </is>
       </c>
       <c r="F10" s="14" t="n">
@@ -773,7 +773,7 @@
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>에이프릴바이오  (편출)</t>
+          <t>삼현  (편출)</t>
         </is>
       </c>
       <c r="F11" s="14" t="n">
@@ -829,7 +829,7 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>LS머트리얼즈</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="F13" s="14" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>87→70</t>
+          <t>236→219</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>LS머트리얼즈</t>
         </is>
       </c>
       <c r="F14" s="14" t="n">
@@ -865,7 +865,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>236→219</t>
+          <t>87→70</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="F56" s="14" t="n">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>42→14</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="F57" s="14" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>978→950</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>삼현</t>
+          <t>HK이노엔  (신규)</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>29→40</t>
+          <t>0→11</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -1868,7 +1868,7 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>HK이노엔  (신규)</t>
+          <t>삼현</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>0→11</t>
+          <t>29→40</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">

--- a/reports/pdf_rolling5_20260630.xlsx
+++ b/reports/pdf_rolling5_20260630.xlsx
@@ -829,7 +829,7 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>LS머트리얼즈</t>
         </is>
       </c>
       <c r="F13" s="14" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>236→219</t>
+          <t>87→70</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>LS머트리얼즈</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="F14" s="14" t="n">
@@ -865,7 +865,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>87→70</t>
+          <t>236→219</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="F56" s="14" t="n">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>978→950</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="F57" s="14" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>42→14</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>52→60</t>
+          <t>60→68</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>알지노믹스  (편출)</t>
         </is>
       </c>
       <c r="F61" s="14" t="n">
@@ -1917,14 +1917,14 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>47→36</t>
+          <t>11→0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>60→68</t>
+          <t>52→60</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>알지노믹스  (편출)</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="F62" s="14" t="n">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>11→0</t>
+          <t>47→36</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260630.xlsx
+++ b/reports/pdf_rolling5_20260630.xlsx
@@ -829,7 +829,7 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>LS머트리얼즈</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="F13" s="14" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>87→70</t>
+          <t>236→219</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>LS머트리얼즈</t>
         </is>
       </c>
       <c r="F14" s="14" t="n">
@@ -865,7 +865,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>236→219</t>
+          <t>87→70</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="F56" s="14" t="n">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>42→14</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="F57" s="14" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>978→950</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
